--- a/salidas/empresas/ETN.xlsx
+++ b/salidas/empresas/ETN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>19.58398056030273</v>
+        <v>19.58398818969727</v>
       </c>
       <c r="C2" t="n">
         <v>33.09999847412109</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>21.70102691650391</v>
+        <v>21.70102310180664</v>
       </c>
       <c r="C4" t="n">
         <v>36.48500061035156</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>22.79544067382812</v>
+        <v>22.79544830322266</v>
       </c>
       <c r="C5" t="n">
         <v>38.32500076293945</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>21.96987342834473</v>
+        <v>21.96987724304199</v>
       </c>
       <c r="C6" t="n">
         <v>36.77000045776367</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>22.52554321289062</v>
+        <v>22.52554702758789</v>
       </c>
       <c r="C7" t="n">
         <v>37.70000076293945</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>19.14969825744629</v>
+        <v>19.14970207214355</v>
       </c>
       <c r="C8" t="n">
         <v>32.04999923706055</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.98779678344727</v>
+        <v>19.98779106140137</v>
       </c>
       <c r="C9" t="n">
         <v>33.25</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.69412994384766</v>
+        <v>20.69412231445312</v>
       </c>
       <c r="C10" t="n">
         <v>34.42499923706055</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>23.29498863220215</v>
+        <v>23.29499626159668</v>
       </c>
       <c r="C12" t="n">
         <v>38.54000091552734</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>22.70869445800781</v>
+        <v>22.70869064331055</v>
       </c>
       <c r="C13" t="n">
         <v>37.56999969482422</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>23.67881011962891</v>
+        <v>23.67880821228027</v>
       </c>
       <c r="C14" t="n">
         <v>39.17499923706055</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>24.61478805541992</v>
+        <v>24.61477279663086</v>
       </c>
       <c r="C15" t="n">
         <v>40.5</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>25.39272308349609</v>
+        <v>25.39271926879883</v>
       </c>
       <c r="C16" t="n">
         <v>41.77999877929688</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.10967826843262</v>
+        <v>27.10968589782715</v>
       </c>
       <c r="C17" t="n">
         <v>44.60499954223633</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>28.62145614624023</v>
+        <v>28.62146186828613</v>
       </c>
       <c r="C18" t="n">
         <v>46.86999893188477</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>28.39551162719727</v>
+        <v>28.39551734924316</v>
       </c>
       <c r="C19" t="n">
         <v>46.5</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>29.67179107666016</v>
+        <v>29.67178726196289</v>
       </c>
       <c r="C20" t="n">
         <v>48.59000015258789</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>28.89382934570312</v>
+        <v>28.89382362365723</v>
       </c>
       <c r="C21" t="n">
         <v>47.11000061035156</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>30.37194061279297</v>
+        <v>30.3719425201416</v>
       </c>
       <c r="C22" t="n">
         <v>49.52000045776367</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.3908863067627</v>
+        <v>28.39090347290039</v>
       </c>
       <c r="C23" t="n">
         <v>46.29000091552734</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>27.51589584350586</v>
+        <v>27.51590347290039</v>
       </c>
       <c r="C24" t="n">
         <v>44.65499877929688</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>29.86974334716797</v>
+        <v>29.8697509765625</v>
       </c>
       <c r="C25" t="n">
         <v>48.47499847412109</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>25.60237312316895</v>
+        <v>25.60236930847168</v>
       </c>
       <c r="C26" t="n">
         <v>41.29499816894531</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>24.99477577209473</v>
+        <v>24.99477767944336</v>
       </c>
       <c r="C27" t="n">
         <v>40.31499862670898</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>27.22983932495117</v>
+        <v>27.22983551025391</v>
       </c>
       <c r="C29" t="n">
         <v>43.91999816894531</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>30.14175033569336</v>
+        <v>30.14175415039062</v>
       </c>
       <c r="C30" t="n">
         <v>48.34000015258789</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>26.49094772338867</v>
+        <v>26.4909553527832</v>
       </c>
       <c r="C31" t="n">
         <v>42.48500061035156</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>22.3016357421875</v>
+        <v>22.30161666870117</v>
       </c>
       <c r="C32" t="n">
         <v>35.52000045776367</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>22.97343826293945</v>
+        <v>22.97343444824219</v>
       </c>
       <c r="C33" t="n">
         <v>36.59000015258789</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>17.6366138458252</v>
+        <v>17.63661956787109</v>
       </c>
       <c r="C34" t="n">
         <v>28.09000015258789</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>14.27459907531738</v>
+        <v>14.2746000289917</v>
       </c>
       <c r="C35" t="n">
         <v>22.47999954223633</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>15.78270053863525</v>
+        <v>15.7827091217041</v>
       </c>
       <c r="C37" t="n">
         <v>24.85499954223633</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.976149559021</v>
+        <v>13.97615242004395</v>
       </c>
       <c r="C38" t="n">
         <v>22.01000022888184</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>11.61170482635498</v>
+        <v>11.61170196533203</v>
       </c>
       <c r="C39" t="n">
         <v>18.07500076293945</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.22922706604004</v>
+        <v>14.22922992706299</v>
       </c>
       <c r="C41" t="n">
         <v>21.89999961853027</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.13176345825195</v>
+        <v>14.1317663192749</v>
       </c>
       <c r="C42" t="n">
         <v>21.75</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.4923677444458</v>
+        <v>14.49236679077148</v>
       </c>
       <c r="C43" t="n">
         <v>22.30500030517578</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.03464889526367</v>
+        <v>17.03466033935547</v>
       </c>
       <c r="C44" t="n">
         <v>25.95999908447266</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>17.7006893157959</v>
+        <v>17.70068740844727</v>
       </c>
       <c r="C45" t="n">
         <v>26.97500038146973</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>18.56685447692871</v>
+        <v>18.56685829162598</v>
       </c>
       <c r="C46" t="n">
         <v>28.29500007629395</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>19.83329963684082</v>
+        <v>19.83330154418945</v>
       </c>
       <c r="C47" t="n">
         <v>30.22500038146973</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.13324165344238</v>
+        <v>21.13323974609375</v>
       </c>
       <c r="C48" t="n">
         <v>31.95000076293945</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>21.04063415527344</v>
+        <v>21.0406436920166</v>
       </c>
       <c r="C49" t="n">
         <v>31.80999946594238</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>20.25351333618164</v>
+        <v>20.25351905822754</v>
       </c>
       <c r="C50" t="n">
         <v>30.6200008392334</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.70416641235352</v>
+        <v>22.70416450500488</v>
       </c>
       <c r="C51" t="n">
         <v>34.06000137329102</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>25.25388336181641</v>
+        <v>25.25388145446777</v>
       </c>
       <c r="C52" t="n">
         <v>37.8849983215332</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>25.71716499328613</v>
+        <v>25.7171516418457</v>
       </c>
       <c r="C53" t="n">
         <v>38.58000183105469</v>
@@ -1470,7 +1482,7 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1489,7 +1501,7 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>26.3259105682373</v>
+        <v>26.32590675354004</v>
       </c>
       <c r="C56" t="n">
         <v>39.22999954223633</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.48169708251953</v>
+        <v>23.48169136047363</v>
       </c>
       <c r="C57" t="n">
         <v>34.7400016784668</v>
@@ -1546,11 +1558,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>27.87859344482422</v>
+        <v>27.87860488891602</v>
       </c>
       <c r="C58" t="n">
         <v>41.24499893188477</v>
@@ -1565,11 +1577,11 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.02127265930176</v>
+        <v>30.02128410339355</v>
       </c>
       <c r="C59" t="n">
         <v>44.41500091552734</v>
@@ -1584,11 +1596,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>32.78702545166016</v>
+        <v>32.78701782226562</v>
       </c>
       <c r="C60" t="n">
         <v>48.20000076293945</v>
@@ -1603,11 +1615,11 @@
       <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>34.52499008178711</v>
+        <v>34.52500152587891</v>
       </c>
       <c r="C61" t="n">
         <v>50.75500106811523</v>
@@ -1622,11 +1634,11 @@
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>36.71874618530273</v>
+        <v>36.7187385559082</v>
       </c>
       <c r="C62" t="n">
         <v>53.97999954223633</v>
@@ -1641,11 +1653,11 @@
       <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>37.91471099853516</v>
+        <v>37.91471481323242</v>
       </c>
       <c r="C63" t="n">
         <v>55.38999938964844</v>
@@ -1660,11 +1672,11 @@
       <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>37.94894790649414</v>
+        <v>37.94894409179688</v>
       </c>
       <c r="C64" t="n">
         <v>55.43999862670898</v>
@@ -1679,11 +1691,11 @@
       <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>36.66208267211914</v>
+        <v>36.66207122802734</v>
       </c>
       <c r="C65" t="n">
         <v>53.56000137329102</v>
@@ -1698,11 +1710,11 @@
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>35.59992599487305</v>
+        <v>35.59992218017578</v>
       </c>
       <c r="C66" t="n">
         <v>51.66999816894531</v>
@@ -1717,11 +1729,11 @@
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>35.44834899902344</v>
+        <v>35.4483642578125</v>
       </c>
       <c r="C67" t="n">
         <v>51.45000076293945</v>
@@ -1736,11 +1748,11 @@
       <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>33.03690338134766</v>
+        <v>33.03689575195312</v>
       </c>
       <c r="C68" t="n">
         <v>47.95000076293945</v>
@@ -1755,11 +1767,11 @@
       <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>29.81486320495605</v>
+        <v>29.81485366821289</v>
       </c>
       <c r="C69" t="n">
         <v>42.95000076293945</v>
@@ -1774,11 +1786,11 @@
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>24.64324951171875</v>
+        <v>24.64324188232422</v>
       </c>
       <c r="C70" t="n">
         <v>35.5</v>
@@ -1793,11 +1805,11 @@
       <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>31.11297225952148</v>
+        <v>31.11296844482422</v>
       </c>
       <c r="C71" t="n">
         <v>44.81999969482422</v>
@@ -1812,11 +1824,11 @@
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>31.41130256652832</v>
+        <v>31.41129875183105</v>
       </c>
       <c r="C72" t="n">
         <v>44.90999984741211</v>
@@ -1831,11 +1843,11 @@
       <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>30.44609069824219</v>
+        <v>30.44608879089355</v>
       </c>
       <c r="C73" t="n">
         <v>43.52999877929688</v>
@@ -1850,11 +1862,11 @@
       <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>34.29294967651367</v>
+        <v>34.29295349121094</v>
       </c>
       <c r="C74" t="n">
         <v>49.02999877929688</v>
@@ -1869,11 +1881,11 @@
       <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>36.78371047973633</v>
+        <v>36.78371429443359</v>
       </c>
       <c r="C75" t="n">
         <v>52.18999862670898</v>
@@ -1888,7 +1900,7 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -1907,11 +1919,11 @@
       <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>33.95744705200195</v>
+        <v>33.95744323730469</v>
       </c>
       <c r="C77" t="n">
         <v>48.18000030517578</v>
@@ -1926,11 +1938,11 @@
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>30.30873680114746</v>
+        <v>30.30873107910156</v>
       </c>
       <c r="C78" t="n">
         <v>42.65999984741211</v>
@@ -1945,11 +1957,11 @@
       <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>28.15600776672363</v>
+        <v>28.156005859375</v>
       </c>
       <c r="C79" t="n">
         <v>39.63000106811523</v>
@@ -1964,11 +1976,11 @@
       <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>31.14708709716797</v>
+        <v>31.14709281921387</v>
       </c>
       <c r="C80" t="n">
         <v>43.84000015258789</v>
@@ -1983,11 +1995,11 @@
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>32.05146026611328</v>
+        <v>32.05146408081055</v>
       </c>
       <c r="C81" t="n">
         <v>44.72000122070312</v>
@@ -2002,11 +2014,11 @@
       <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>33.87908554077148</v>
+        <v>33.87907409667969</v>
       </c>
       <c r="C82" t="n">
         <v>47.27000045776367</v>
@@ -2021,11 +2033,11 @@
       <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>34.12126159667969</v>
+        <v>34.12123870849609</v>
       </c>
       <c r="C83" t="n">
         <v>47.22000122070312</v>
@@ -2040,11 +2052,11 @@
       <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>37.69089889526367</v>
+        <v>37.6909065246582</v>
       </c>
       <c r="C84" t="n">
         <v>52.15999984741211</v>
@@ -2059,11 +2071,11 @@
       <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>39.15056610107422</v>
+        <v>39.15056228637695</v>
       </c>
       <c r="C85" t="n">
         <v>54.18000030517578</v>
@@ -2078,11 +2090,11 @@
       <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>41.15216827392578</v>
+        <v>41.15216445922852</v>
       </c>
       <c r="C86" t="n">
         <v>56.95000076293945</v>
@@ -2097,7 +2109,7 @@
       <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2122,7 +2134,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2147,11 +2159,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>44.67459869384766</v>
+        <v>44.67462158203125</v>
       </c>
       <c r="C89" t="n">
         <v>61.40999984741211</v>
@@ -2172,11 +2184,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>48.40036010742188</v>
+        <v>48.40036773681641</v>
       </c>
       <c r="C90" t="n">
         <v>66.05999755859375</v>
@@ -2197,11 +2209,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>48.21721649169922</v>
+        <v>48.21720886230469</v>
       </c>
       <c r="C91" t="n">
         <v>65.80999755859375</v>
@@ -2222,11 +2234,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>50.51779556274414</v>
+        <v>50.51778411865234</v>
       </c>
       <c r="C92" t="n">
         <v>68.94999694824219</v>
@@ -2247,11 +2259,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>46.67717361450195</v>
+        <v>46.67716217041016</v>
       </c>
       <c r="C93" t="n">
         <v>63.31999969482422</v>
@@ -2272,11 +2284,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>50.74630737304688</v>
+        <v>50.74631118774414</v>
       </c>
       <c r="C94" t="n">
         <v>68.83999633789062</v>
@@ -2297,11 +2309,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>52.32247543334961</v>
+        <v>52.32248306274414</v>
       </c>
       <c r="C95" t="n">
         <v>70.55999755859375</v>
@@ -2322,11 +2334,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>53.87971878051758</v>
+        <v>53.87971115112305</v>
       </c>
       <c r="C96" t="n">
         <v>72.66000366210938</v>
@@ -2347,11 +2359,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>56.4454231262207</v>
+        <v>56.44541549682617</v>
       </c>
       <c r="C97" t="n">
         <v>76.12000274658203</v>
@@ -2372,11 +2384,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>54.19856262207031</v>
+        <v>54.19855880737305</v>
       </c>
       <c r="C98" t="n">
         <v>73.08999633789062</v>
@@ -2397,11 +2409,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>55.39987182617188</v>
+        <v>55.39984893798828</v>
       </c>
       <c r="C99" t="n">
         <v>74.70999908447266</v>
@@ -2426,11 +2438,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>56.07318496704102</v>
+        <v>56.07316970825195</v>
       </c>
       <c r="C100" t="n">
         <v>75.12000274658203</v>
@@ -2455,11 +2467,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>54.22197341918945</v>
+        <v>54.22197723388672</v>
       </c>
       <c r="C101" t="n">
         <v>72.63999938964844</v>
@@ -2484,11 +2496,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>55.37934112548828</v>
+        <v>55.37932586669922</v>
       </c>
       <c r="C102" t="n">
         <v>73.69000244140625</v>
@@ -2513,11 +2525,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>58.00211715698242</v>
+        <v>58.00212097167969</v>
       </c>
       <c r="C103" t="n">
         <v>77.18000030517578</v>
@@ -2542,11 +2554,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>51.40340423583984</v>
+        <v>51.40341186523438</v>
       </c>
       <c r="C104" t="n">
         <v>67.91999816894531</v>
@@ -2571,11 +2583,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>52.83378219604492</v>
+        <v>52.83380508422852</v>
       </c>
       <c r="C105" t="n">
         <v>69.80999755859375</v>
@@ -2600,11 +2612,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>47.95986175537109</v>
+        <v>47.95986557006836</v>
       </c>
       <c r="C106" t="n">
         <v>63.36999893188477</v>
@@ -2629,11 +2641,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>51.75910949707031</v>
+        <v>51.75909805297852</v>
       </c>
       <c r="C107" t="n">
         <v>68.38999938964844</v>
@@ -2658,7 +2670,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -2687,7 +2699,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -2716,11 +2728,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>48.09225463867188</v>
+        <v>48.0922737121582</v>
       </c>
       <c r="C110" t="n">
         <v>63.09000015258789</v>
@@ -2745,11 +2757,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>54.12952423095703</v>
+        <v>54.1295280456543</v>
       </c>
       <c r="C111" t="n">
         <v>71.01000213623047</v>
@@ -2774,11 +2786,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>52.20153427124023</v>
+        <v>52.20154571533203</v>
       </c>
       <c r="C112" t="n">
         <v>67.94000244140625</v>
@@ -2803,11 +2815,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>53.22953796386719</v>
+        <v>53.22954177856445</v>
       </c>
       <c r="C113" t="n">
         <v>68.73000335693359</v>
@@ -2832,11 +2844,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>55.44453811645508</v>
+        <v>55.44451904296875</v>
       </c>
       <c r="C114" t="n">
         <v>71.58999633789062</v>
@@ -2861,11 +2873,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>52.26919555664062</v>
+        <v>52.26920318603516</v>
       </c>
       <c r="C115" t="n">
         <v>67.48999786376953</v>
@@ -2890,7 +2902,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -2919,11 +2931,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>44.5882682800293</v>
+        <v>44.5882453918457</v>
       </c>
       <c r="C117" t="n">
         <v>57.06000137329102</v>
@@ -2948,11 +2960,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>40.08723068237305</v>
+        <v>40.08722686767578</v>
       </c>
       <c r="C118" t="n">
         <v>51.29999923706055</v>
@@ -2977,11 +2989,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>43.68961715698242</v>
+        <v>43.68961334228516</v>
       </c>
       <c r="C119" t="n">
         <v>55.90999984741211</v>
@@ -3006,11 +3018,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>45.8926887512207</v>
+        <v>45.89268112182617</v>
       </c>
       <c r="C120" t="n">
         <v>58.15999984741211</v>
@@ -3035,7 +3047,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3064,11 +3076,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>39.85626220703125</v>
+        <v>39.85623931884766</v>
       </c>
       <c r="C122" t="n">
         <v>50.5099983215332</v>
@@ -3093,7 +3105,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3122,11 +3134,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>49.85499954223633</v>
+        <v>49.85499572753906</v>
       </c>
       <c r="C124" t="n">
         <v>62.56000137329102</v>
@@ -3151,11 +3163,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>50.42079925537109</v>
+        <v>50.42080688476562</v>
       </c>
       <c r="C125" t="n">
         <v>63.27000045776367</v>
@@ -3180,11 +3192,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>49.56021118164062</v>
+        <v>49.56021881103516</v>
       </c>
       <c r="C126" t="n">
         <v>61.63000106811523</v>
@@ -3209,11 +3221,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>48.03231048583984</v>
+        <v>48.03231811523438</v>
       </c>
       <c r="C127" t="n">
         <v>59.72999954223633</v>
@@ -3238,11 +3250,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>50.99160385131836</v>
+        <v>50.99161148071289</v>
       </c>
       <c r="C128" t="n">
         <v>63.40999984741211</v>
@@ -3267,11 +3279,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>53.98939895629883</v>
+        <v>53.9893913269043</v>
       </c>
       <c r="C129" t="n">
         <v>66.54000091552734</v>
@@ -3296,11 +3308,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>53.31594467163086</v>
+        <v>53.31593704223633</v>
       </c>
       <c r="C130" t="n">
         <v>65.70999908447266</v>
@@ -3325,11 +3337,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>51.74185562133789</v>
+        <v>51.74186325073242</v>
       </c>
       <c r="C131" t="n">
         <v>63.77000045776367</v>
@@ -3354,11 +3366,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>54.47509002685547</v>
+        <v>54.47509384155273</v>
       </c>
       <c r="C132" t="n">
         <v>66.51000213623047</v>
@@ -3383,11 +3395,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>54.95013046264648</v>
+        <v>54.95013809204102</v>
       </c>
       <c r="C133" t="n">
         <v>67.08999633789062</v>
@@ -3412,11 +3424,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>57.97243118286133</v>
+        <v>57.97246551513672</v>
       </c>
       <c r="C134" t="n">
         <v>70.77999877929688</v>
@@ -3441,11 +3453,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>58.95530319213867</v>
+        <v>58.95528793334961</v>
       </c>
       <c r="C135" t="n">
         <v>71.98000335693359</v>
@@ -3470,11 +3482,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>61.23427200317383</v>
+        <v>61.23430252075195</v>
       </c>
       <c r="C136" t="n">
         <v>74.15000152587891</v>
@@ -3499,11 +3511,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>62.4647102355957</v>
+        <v>62.46472549438477</v>
       </c>
       <c r="C137" t="n">
         <v>75.63999938964844</v>
@@ -3528,11 +3540,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>64.40281677246094</v>
+        <v>64.40277862548828</v>
       </c>
       <c r="C138" t="n">
         <v>77.37999725341797</v>
@@ -3557,7 +3569,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3586,11 +3598,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>65.12689208984375</v>
+        <v>65.12687683105469</v>
       </c>
       <c r="C140" t="n">
         <v>78.25</v>
@@ -3615,11 +3627,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>60.21179962158203</v>
+        <v>60.21180725097656</v>
       </c>
       <c r="C141" t="n">
         <v>71.76000213623047</v>
@@ -3644,11 +3656,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>64.43233489990234</v>
+        <v>64.43231964111328</v>
       </c>
       <c r="C142" t="n">
         <v>76.79000091552734</v>
@@ -3673,11 +3685,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>67.14253234863281</v>
+        <v>67.14255523681641</v>
       </c>
       <c r="C143" t="n">
         <v>80.01999664306641</v>
@@ -3702,11 +3714,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>65.74695587158203</v>
+        <v>65.74699401855469</v>
       </c>
       <c r="C144" t="n">
         <v>77.77999877929688</v>
@@ -3731,11 +3743,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>66.78668975830078</v>
+        <v>66.78667449951172</v>
       </c>
       <c r="C145" t="n">
         <v>79.01000213623047</v>
@@ -3760,11 +3772,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>70.97936248779297</v>
+        <v>70.9793701171875</v>
       </c>
       <c r="C146" t="n">
         <v>83.97000122070312</v>
@@ -3789,7 +3801,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -3818,11 +3830,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>68.10139465332031</v>
+        <v>68.10138702392578</v>
       </c>
       <c r="C148" t="n">
         <v>79.91000366210938</v>
@@ -3847,7 +3859,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -3876,11 +3888,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>65.86040496826172</v>
+        <v>65.86041259765625</v>
       </c>
       <c r="C150" t="n">
         <v>76.58000183105469</v>
@@ -3905,7 +3917,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -3934,7 +3946,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -3963,7 +3975,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -3992,11 +4004,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>74.58960723876953</v>
+        <v>74.58959197998047</v>
       </c>
       <c r="C154" t="n">
         <v>86.73000335693359</v>
@@ -4021,11 +4033,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>61.63769149780273</v>
+        <v>61.6376953125</v>
       </c>
       <c r="C155" t="n">
         <v>71.66999816894531</v>
@@ -4050,11 +4062,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>66.17003631591797</v>
+        <v>66.17001342773438</v>
       </c>
       <c r="C156" t="n">
         <v>76.94000244140625</v>
@@ -4079,11 +4091,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>59.04903030395508</v>
+        <v>59.04903793334961</v>
       </c>
       <c r="C157" t="n">
         <v>68.66000366210938</v>
@@ -4108,11 +4120,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>65.57660675048828</v>
+        <v>65.57658386230469</v>
       </c>
       <c r="C158" t="n">
         <v>76.25</v>
@@ -4137,11 +4149,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>68.60385131835938</v>
+        <v>68.60387420654297</v>
       </c>
       <c r="C159" t="n">
         <v>79.76999664306641</v>
@@ -4166,11 +4178,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>69.89632415771484</v>
+        <v>69.89633178710938</v>
       </c>
       <c r="C160" t="n">
         <v>80.55999755859375</v>
@@ -4195,11 +4207,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>71.85719299316406</v>
+        <v>71.85717010498047</v>
       </c>
       <c r="C161" t="n">
         <v>82.81999969482422</v>
@@ -4224,11 +4236,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>65.19492340087891</v>
+        <v>65.19493103027344</v>
       </c>
       <c r="C162" t="n">
         <v>74.48999786376953</v>
@@ -4253,11 +4265,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>72.88807678222656</v>
+        <v>72.88809967041016</v>
       </c>
       <c r="C163" t="n">
         <v>83.27999877929688</v>
@@ -4282,7 +4294,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4311,7 +4323,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4340,11 +4352,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>73.40845489501953</v>
+        <v>73.40843963623047</v>
       </c>
       <c r="C166" t="n">
         <v>83.15000152587891</v>
@@ -4369,11 +4381,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>77.52825164794922</v>
+        <v>77.52822875976562</v>
       </c>
       <c r="C167" t="n">
         <v>87.11000061035156</v>
@@ -4398,11 +4410,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>82.32536315917969</v>
+        <v>82.32538604736328</v>
       </c>
       <c r="C168" t="n">
         <v>92.5</v>
@@ -4427,11 +4439,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>84.30117034912109</v>
+        <v>84.30119323730469</v>
       </c>
       <c r="C169" t="n">
         <v>94.72000122070312</v>
@@ -4456,7 +4468,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4485,11 +4497,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>80.74116516113281</v>
+        <v>80.74117279052734</v>
       </c>
       <c r="C171" t="n">
         <v>90.72000122070312</v>
@@ -4514,11 +4526,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>69.74790954589844</v>
+        <v>69.74790191650391</v>
       </c>
       <c r="C172" t="n">
         <v>77.69000244140625</v>
@@ -4543,11 +4555,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>74.96395111083984</v>
+        <v>74.96396636962891</v>
       </c>
       <c r="C173" t="n">
         <v>83.5</v>
@@ -4572,11 +4584,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>76.29276275634766</v>
+        <v>76.29273223876953</v>
       </c>
       <c r="C174" t="n">
         <v>84.90000152587891</v>
@@ -4601,11 +4613,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>78.61117553710938</v>
+        <v>78.61119079589844</v>
       </c>
       <c r="C175" t="n">
         <v>87.48000335693359</v>
@@ -4630,7 +4642,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -4659,11 +4671,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>92.40677642822266</v>
+        <v>92.40676116943359</v>
       </c>
       <c r="C177" t="n">
         <v>102.0999984741211</v>
@@ -4688,7 +4700,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -4717,11 +4729,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>93.93630981445312</v>
+        <v>93.93634796142578</v>
       </c>
       <c r="C179" t="n">
         <v>103.7900009155273</v>
@@ -4746,7 +4758,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -4775,7 +4787,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -4804,7 +4816,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -4833,11 +4845,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>118.6478118896484</v>
+        <v>118.6478271484375</v>
       </c>
       <c r="C183" t="n">
         <v>130.1900024414062</v>
@@ -4862,11 +4874,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>126.7046661376953</v>
+        <v>126.7045974731445</v>
       </c>
       <c r="C184" t="n">
         <v>138.2799987792969</v>
@@ -4891,11 +4903,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>130.9653930664062</v>
+        <v>130.9654235839844</v>
       </c>
       <c r="C185" t="n">
         <v>142.9299926757812</v>
@@ -4920,11 +4932,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>133.7989196777344</v>
+        <v>133.798828125</v>
       </c>
       <c r="C186" t="n">
         <v>145.25</v>
@@ -4949,11 +4961,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>136.4978485107422</v>
+        <v>136.4978790283203</v>
       </c>
       <c r="C187" t="n">
         <v>148.1799926757812</v>
@@ -4978,11 +4990,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>145.5897827148438</v>
+        <v>145.5897216796875</v>
       </c>
       <c r="C188" t="n">
         <v>158.0500030517578</v>
@@ -5007,11 +5019,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>155.7963256835938</v>
+        <v>155.7963562011719</v>
       </c>
       <c r="C189" t="n">
         <v>168.3600006103516</v>
@@ -5036,11 +5048,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>138.1679229736328</v>
+        <v>138.1679534912109</v>
       </c>
       <c r="C190" t="n">
         <v>149.3099975585938</v>
@@ -5065,11 +5077,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>152.4650115966797</v>
+        <v>152.4649505615234</v>
       </c>
       <c r="C191" t="n">
         <v>164.7599945068359</v>
@@ -5094,11 +5106,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>150.621826171875</v>
+        <v>150.6219024658203</v>
       </c>
       <c r="C192" t="n">
         <v>162.0599975585938</v>
@@ -5123,11 +5135,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>160.6224212646484</v>
+        <v>160.6224517822266</v>
       </c>
       <c r="C193" t="n">
         <v>172.8200073242188</v>
@@ -5152,11 +5164,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>147.2480926513672</v>
+        <v>147.2480773925781</v>
       </c>
       <c r="C194" t="n">
         <v>158.4299926757812</v>
@@ -5181,11 +5193,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>143.4002532958984</v>
+        <v>143.4002838134766</v>
       </c>
       <c r="C195" t="n">
         <v>154.2899932861328</v>
@@ -5210,11 +5222,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>141.8191986083984</v>
+        <v>141.8191833496094</v>
       </c>
       <c r="C196" t="n">
         <v>151.7599945068359</v>
@@ -5239,7 +5251,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5268,11 +5280,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>130.2705688476562</v>
+        <v>130.2705841064453</v>
       </c>
       <c r="C198" t="n">
         <v>138.6000061035156</v>
@@ -5297,7 +5309,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5326,11 +5338,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>139.4722290039062</v>
+        <v>139.4722442626953</v>
       </c>
       <c r="C200" t="n">
         <v>148.3899993896484</v>
@@ -5355,7 +5367,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5384,11 +5396,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>126.0290679931641</v>
+        <v>126.0290222167969</v>
       </c>
       <c r="C202" t="n">
         <v>133.3600006103516</v>
@@ -5413,11 +5425,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>141.8204803466797</v>
+        <v>141.8205261230469</v>
       </c>
       <c r="C203" t="n">
         <v>150.0700073242188</v>
@@ -5442,11 +5454,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>155.2599945068359</v>
+        <v>155.2599639892578</v>
       </c>
       <c r="C204" t="n">
         <v>163.4499969482422</v>
@@ -5471,11 +5483,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>149.0856475830078</v>
+        <v>149.0856628417969</v>
       </c>
       <c r="C205" t="n">
         <v>156.9499969482422</v>
@@ -5500,7 +5512,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5529,7 +5541,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5558,7 +5570,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5587,7 +5599,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5616,7 +5628,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5645,11 +5657,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>192.9511413574219</v>
+        <v>192.9511566162109</v>
       </c>
       <c r="C211" t="n">
         <v>201.1000061035156</v>
@@ -5674,11 +5686,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>197.0001525878906</v>
+        <v>197.0001678466797</v>
       </c>
       <c r="C212" t="n">
         <v>205.3200073242188</v>
@@ -5703,11 +5715,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>221.9141387939453</v>
+        <v>221.9141235351562</v>
       </c>
       <c r="C213" t="n">
         <v>230.3699951171875</v>
@@ -5732,11 +5744,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>205.4514770507812</v>
+        <v>205.4514617919922</v>
       </c>
       <c r="C214" t="n">
         <v>213.2799987792969</v>
@@ -5761,11 +5773,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>200.2785949707031</v>
+        <v>200.278564453125</v>
       </c>
       <c r="C215" t="n">
         <v>207.9100036621094</v>
@@ -5790,11 +5802,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>220.2086334228516</v>
+        <v>220.2086486816406</v>
       </c>
       <c r="C216" t="n">
         <v>227.6900024414062</v>
@@ -5819,7 +5831,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -5848,11 +5860,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>237.994384765625</v>
+        <v>237.9944000244141</v>
       </c>
       <c r="C218" t="n">
         <v>246.0800018310547</v>
@@ -5877,11 +5889,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>279.504150390625</v>
+        <v>279.5041809082031</v>
       </c>
       <c r="C219" t="n">
         <v>289</v>
@@ -5906,7 +5918,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -5935,11 +5947,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>308.7666015625</v>
+        <v>308.7665100097656</v>
       </c>
       <c r="C221" t="n">
         <v>318.260009765625</v>
@@ -5964,11 +5976,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>323.8870544433594</v>
+        <v>323.8869934082031</v>
       </c>
       <c r="C222" t="n">
         <v>332.8500061035156</v>
@@ -5993,11 +6005,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>305.1067199707031</v>
+        <v>305.1067504882812</v>
       </c>
       <c r="C223" t="n">
         <v>313.5499877929688</v>
@@ -6022,11 +6034,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>296.5826721191406</v>
+        <v>296.5826416015625</v>
       </c>
       <c r="C224" t="n">
         <v>304.7900085449219</v>
@@ -6051,11 +6063,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>299.6700744628906</v>
+        <v>299.6701049804688</v>
       </c>
       <c r="C225" t="n">
         <v>306.9299926757812</v>
@@ -6080,11 +6092,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>323.6003723144531</v>
+        <v>323.600341796875</v>
       </c>
       <c r="C226" t="n">
         <v>331.4400024414062</v>
@@ -6109,11 +6121,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>323.737060546875</v>
+        <v>323.7370300292969</v>
       </c>
       <c r="C227" t="n">
         <v>331.5799865722656</v>
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6167,7 +6179,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6196,11 +6208,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>319.615478515625</v>
+        <v>319.6154479980469</v>
       </c>
       <c r="C230" t="n">
         <v>326.4400024414062</v>
@@ -6225,11 +6237,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>287.1878967285156</v>
+        <v>287.1878662109375</v>
       </c>
       <c r="C231" t="n">
         <v>293.3200073242188</v>
@@ -6254,11 +6266,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>267.1218872070312</v>
+        <v>267.1219177246094</v>
       </c>
       <c r="C232" t="n">
         <v>271.8299865722656</v>
@@ -6283,11 +6295,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>289.2715454101562</v>
+        <v>289.2715759277344</v>
       </c>
       <c r="C233" t="n">
         <v>294.3699951171875</v>
@@ -6312,11 +6324,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>315.7498779296875</v>
+        <v>315.7498168945312</v>
       </c>
       <c r="C234" t="n">
         <v>320.2000122070312</v>
@@ -6341,7 +6353,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6370,11 +6382,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>379.3731384277344</v>
+        <v>379.3731079101562</v>
       </c>
       <c r="C236" t="n">
         <v>384.7200012207031</v>
@@ -6399,7 +6411,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6428,11 +6440,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>370.1233825683594</v>
+        <v>370.1233520507812</v>
       </c>
       <c r="C238" t="n">
         <v>374.25</v>
@@ -6457,7 +6469,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6486,11 +6498,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>343.0205993652344</v>
+        <v>343.0205688476562</v>
       </c>
       <c r="C240" t="n">
         <v>345.8900146484375</v>
@@ -6515,11 +6527,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>315.8677062988281</v>
+        <v>315.8677368164062</v>
       </c>
       <c r="C241" t="n">
         <v>318.510009765625</v>
@@ -6544,7 +6556,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6573,11 +6585,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>372.8014831542969</v>
+        <v>372.8014526367188</v>
       </c>
       <c r="C243" t="n">
         <v>375.9200134277344</v>
@@ -6602,7 +6614,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6631,7 +6643,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6660,7 +6672,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6689,7 +6701,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6718,7 +6730,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6747,7 +6759,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -6776,32 +6788,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>438.760009765625</v>
+        <v>440</v>
       </c>
       <c r="C250" t="n">
-        <v>438.760009765625</v>
+        <v>440</v>
       </c>
       <c r="D250" t="n">
-        <v>34750100</v>
+        <v>36112100</v>
       </c>
       <c r="E250" t="n">
         <v>9.82</v>
       </c>
       <c r="F250" t="n">
-        <v>44.68024539364816</v>
+        <v>44.80651731160896</v>
       </c>
       <c r="G250" t="n">
         <v>388400000</v>
       </c>
       <c r="H250" t="n">
-        <v>170414387792.9688</v>
+        <v>170896000000</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08946987641606591</v>
+        <v>0.09297657054582904</v>
       </c>
     </row>
   </sheetData>
@@ -6833,75 +6845,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6937,13 +6949,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6979,13 +6991,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7021,13 +7033,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7063,13 +7075,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7105,13 +7117,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7147,13 +7159,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7180,7 +7192,7 @@
       <c r="I8" t="n">
         <v>3.899999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="K8" t="n">
@@ -7193,13 +7205,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7226,7 +7238,7 @@
       <c r="I9" t="n">
         <v>4.029999999999999</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="K9" t="n">
@@ -7239,13 +7251,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7272,7 +7284,7 @@
       <c r="I10" t="n">
         <v>3.35</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K10" t="n">
@@ -7285,13 +7297,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7318,7 +7330,7 @@
       <c r="I11" t="n">
         <v>3.539999999999999</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="K11" t="n">
@@ -7331,13 +7343,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7364,7 +7376,7 @@
       <c r="I12" t="n">
         <v>3.76</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K12" t="n">
@@ -7377,13 +7389,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7410,7 +7422,7 @@
       <c r="I13" t="n">
         <v>3.83</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K13" t="n">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7456,7 +7468,7 @@
       <c r="I14" t="n">
         <v>4.609999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K14" t="n">
@@ -7469,13 +7481,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7502,7 +7514,7 @@
       <c r="I15" t="n">
         <v>4.31</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K15" t="n">
@@ -7515,13 +7527,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7548,7 +7560,7 @@
       <c r="I16" t="n">
         <v>4.23</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="K16" t="n">
@@ -7561,13 +7573,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7594,7 +7606,7 @@
       <c r="I17" t="n">
         <v>4.12</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K17" t="n">
@@ -7607,13 +7619,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7640,7 +7652,7 @@
       <c r="I18" t="n">
         <v>4.050000000000001</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="K18" t="n">
@@ -7653,13 +7665,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7686,7 +7698,7 @@
       <c r="I19" t="n">
         <v>4.24</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K19" t="n">
@@ -7699,13 +7711,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7732,7 +7744,7 @@
       <c r="I20" t="n">
         <v>4.21</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="K20" t="n">
@@ -7745,13 +7757,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7778,7 +7790,7 @@
       <c r="I21" t="n">
         <v>4.289999999999999</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="K21" t="n">
@@ -7791,13 +7803,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -7824,7 +7836,7 @@
       <c r="I22" t="n">
         <v>4.369999999999999</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="K22" t="n">
@@ -7837,13 +7849,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -7870,7 +7882,7 @@
       <c r="I23" t="n">
         <v>6.359999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="K23" t="n">
@@ -7883,13 +7895,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -7916,7 +7928,7 @@
       <c r="I24" t="n">
         <v>6.68</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="K24" t="n">
@@ -7929,13 +7941,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7962,7 +7974,7 @@
       <c r="I25" t="n">
         <v>6.819999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="K25" t="n">
@@ -7975,13 +7987,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8008,7 +8020,7 @@
       <c r="I26" t="n">
         <v>7.06</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="K26" t="n">
@@ -8021,13 +8033,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8054,7 +8066,7 @@
       <c r="I27" t="n">
         <v>4.869999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K27" t="n">
@@ -8067,13 +8079,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8100,7 +8112,7 @@
       <c r="I28" t="n">
         <v>4.91</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="K28" t="n">
@@ -8113,13 +8125,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8146,7 +8158,7 @@
       <c r="I29" t="n">
         <v>5.039999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K29" t="n">
@@ -8159,13 +8171,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8192,7 +8204,7 @@
       <c r="I30" t="n">
         <v>5.15</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="K30" t="n">
@@ -8205,13 +8217,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8238,7 +8250,7 @@
       <c r="I31" t="n">
         <v>5.64</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="K31" t="n">
@@ -8251,13 +8263,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8284,7 +8296,7 @@
       <c r="I32" t="n">
         <v>5.25</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="K32" t="n">
@@ -8297,13 +8309,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8330,7 +8342,7 @@
       <c r="I33" t="n">
         <v>5.09</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="K33" t="n">
@@ -8343,13 +8355,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8376,7 +8388,7 @@
       <c r="I34" t="n">
         <v>3.72</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K34" t="n">
@@ -8389,13 +8401,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8422,7 +8434,7 @@
       <c r="I35" t="n">
         <v>3.39</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="K35" t="n">
@@ -8435,13 +8447,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8468,7 +8480,7 @@
       <c r="I36" t="n">
         <v>3.49</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="K36" t="n">
@@ -8481,13 +8493,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8514,7 +8526,7 @@
       <c r="I37" t="n">
         <v>3.56</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="K37" t="n">
@@ -8527,13 +8539,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8560,7 +8572,7 @@
       <c r="I38" t="n">
         <v>4.69</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="K38" t="n">
@@ -8573,13 +8585,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8606,7 +8618,7 @@
       <c r="I39" t="n">
         <v>5.149999999999999</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="K39" t="n">
@@ -8619,13 +8631,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8652,7 +8664,7 @@
       <c r="I40" t="n">
         <v>5.34</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K40" t="n">
@@ -8665,13 +8677,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8698,7 +8710,7 @@
       <c r="I41" t="n">
         <v>5.53</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K41" t="n">
@@ -8711,13 +8723,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8744,7 +8756,7 @@
       <c r="I42" t="n">
         <v>5.77</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K42" t="n">
@@ -8757,13 +8769,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -8790,7 +8802,7 @@
       <c r="I43" t="n">
         <v>5.720000000000001</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="K43" t="n">
@@ -8803,13 +8815,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -8836,7 +8848,7 @@
       <c r="I44" t="n">
         <v>6.140000000000001</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K44" t="n">
@@ -8849,13 +8861,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -8882,7 +8894,7 @@
       <c r="I45" t="n">
         <v>6.4</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K45" t="n">
@@ -8895,13 +8907,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -8928,7 +8940,7 @@
       <c r="I46" t="n">
         <v>6.760000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="K46" t="n">
@@ -8941,13 +8953,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -8974,7 +8986,7 @@
       <c r="I47" t="n">
         <v>7.46</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K47" t="n">
@@ -8987,13 +8999,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9020,7 +9032,7 @@
       <c r="I48" t="n">
         <v>8.02</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="K48" t="n">
@@ -9033,13 +9045,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9066,7 +9078,7 @@
       <c r="I49" t="n">
         <v>8.469999999999999</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K49" t="n">
@@ -9079,13 +9091,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9112,7 +9124,7 @@
       <c r="I50" t="n">
         <v>9.09</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K50" t="n">
@@ -9125,13 +9137,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9158,7 +9170,7 @@
       <c r="I51" t="n">
         <v>9.399999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K51" t="n">
@@ -9171,13 +9183,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9204,7 +9216,7 @@
       <c r="I52" t="n">
         <v>9.5</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K52" t="n">
@@ -9217,13 +9229,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9250,7 +9262,7 @@
       <c r="I53" t="n">
         <v>9.91</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K53" t="n">
@@ -9263,13 +9275,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9296,7 +9308,7 @@
       <c r="I54" t="n">
         <v>9.940000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K54" t="n">
@@ -9309,13 +9321,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9342,7 +9354,7 @@
       <c r="I55" t="n">
         <v>10</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K55" t="n">
@@ -9355,13 +9367,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9388,7 +9400,7 @@
       <c r="I56" t="n">
         <v>10.45</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="K56" t="n">
@@ -9401,13 +9413,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9434,7 +9446,7 @@
       <c r="I57" t="n">
         <v>10.22</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K57" t="n">
@@ -9447,13 +9459,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9480,7 +9492,7 @@
       <c r="I58" t="n">
         <v>9.82</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K58" t="n">
@@ -9517,52 +9529,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C2" t="n">
@@ -9591,10 +9603,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C3" t="n">
@@ -9623,10 +9635,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C4" t="n">
@@ -9655,10 +9667,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C5" t="n">
@@ -9687,10 +9699,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="C6" t="n">
@@ -9719,10 +9731,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="C7" t="n">
@@ -9751,10 +9763,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C8" t="n">
@@ -9783,10 +9795,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="C9" t="n">
@@ -9815,10 +9827,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="C10" t="n">
@@ -9847,10 +9859,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C11" t="n">
@@ -9879,10 +9891,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C12" t="n">
@@ -9911,10 +9923,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C13" t="n">
@@ -9943,10 +9955,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C14" t="n">
@@ -9975,10 +9987,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C15" t="n">
@@ -10007,10 +10019,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="C16" t="n">
@@ -10039,10 +10051,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C17" t="n">
@@ -10071,10 +10083,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="C18" t="n">
@@ -10103,10 +10115,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C19" t="n">
@@ -10135,10 +10147,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C20" t="n">
@@ -10167,10 +10179,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="C21" t="n">
@@ -10199,10 +10211,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C22" t="n">
@@ -10231,10 +10243,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C23" t="n">
@@ -10263,10 +10275,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="C24" t="n">
@@ -10295,10 +10307,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C25" t="n">
@@ -10327,10 +10339,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="C26" t="n">
@@ -10359,10 +10371,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C27" t="n">
@@ -10391,10 +10403,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="C28" t="n">
@@ -10423,10 +10435,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="C29" t="n">
@@ -10455,10 +10467,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="C30" t="n">
@@ -10487,10 +10499,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C31" t="n">
@@ -10519,10 +10531,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C32" t="n">
@@ -10551,10 +10563,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="C33" t="n">
@@ -10583,10 +10595,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="C34" t="n">
@@ -10615,10 +10627,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="C35" t="n">
@@ -10647,10 +10659,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="C36" t="n">
@@ -10679,10 +10691,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="C37" t="n">
@@ -10711,10 +10723,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C38" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C39" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C40" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C41" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C42" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C43" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C44" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C45" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="C46" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C47" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C48" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C49" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C50" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C51" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C52" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C53" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="C54" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C55" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C56" t="n">
@@ -11337,12 +11349,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/ETN.xlsx
+++ b/salidas/empresas/ETN.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>19.58398818969727</v>
+        <v>19.58398246765137</v>
       </c>
       <c r="C2" t="n">
         <v>33.09999847412109</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>20.7196159362793</v>
+        <v>20.71960639953613</v>
       </c>
       <c r="C3" t="n">
         <v>34.83499908447266</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>21.70102310180664</v>
+        <v>21.70102119445801</v>
       </c>
       <c r="C4" t="n">
         <v>36.48500061035156</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>22.79544830322266</v>
+        <v>22.79543685913086</v>
       </c>
       <c r="C5" t="n">
         <v>38.32500076293945</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>21.96987724304199</v>
+        <v>21.96987342834473</v>
       </c>
       <c r="C6" t="n">
         <v>36.77000045776367</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>22.52554702758789</v>
+        <v>22.52553939819336</v>
       </c>
       <c r="C7" t="n">
         <v>37.70000076293945</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>19.14970207214355</v>
+        <v>19.14969444274902</v>
       </c>
       <c r="C8" t="n">
         <v>32.04999923706055</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.98779106140137</v>
+        <v>19.98779296875</v>
       </c>
       <c r="C9" t="n">
         <v>33.25</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.69412231445312</v>
+        <v>20.69413185119629</v>
       </c>
       <c r="C10" t="n">
         <v>34.42499923706055</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>23.29499626159668</v>
+        <v>23.29499816894531</v>
       </c>
       <c r="C12" t="n">
         <v>38.54000091552734</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>22.70869064331055</v>
+        <v>22.70869255065918</v>
       </c>
       <c r="C13" t="n">
         <v>37.56999969482422</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>23.67880821228027</v>
+        <v>23.6788158416748</v>
       </c>
       <c r="C14" t="n">
         <v>39.17499923706055</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>24.61477279663086</v>
+        <v>24.61478614807129</v>
       </c>
       <c r="C15" t="n">
         <v>40.5</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>25.39271926879883</v>
+        <v>25.39273071289062</v>
       </c>
       <c r="C16" t="n">
         <v>41.77999877929688</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.10968589782715</v>
+        <v>27.10968399047852</v>
       </c>
       <c r="C17" t="n">
         <v>44.60499954223633</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>29.67178726196289</v>
+        <v>29.67179107666016</v>
       </c>
       <c r="C20" t="n">
         <v>48.59000015258789</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>28.89382362365723</v>
+        <v>28.89381980895996</v>
       </c>
       <c r="C21" t="n">
         <v>47.11000061035156</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>30.3719425201416</v>
+        <v>30.37194442749023</v>
       </c>
       <c r="C22" t="n">
         <v>49.52000045776367</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.39090347290039</v>
+        <v>28.39089393615723</v>
       </c>
       <c r="C23" t="n">
         <v>46.29000091552734</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>29.8697509765625</v>
+        <v>29.86974716186523</v>
       </c>
       <c r="C25" t="n">
         <v>48.47499847412109</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>25.60236930847168</v>
+        <v>25.60236167907715</v>
       </c>
       <c r="C26" t="n">
         <v>41.29499816894531</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>24.99477767944336</v>
+        <v>24.99478340148926</v>
       </c>
       <c r="C27" t="n">
         <v>40.31499862670898</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>24.69718551635742</v>
+        <v>24.69718742370605</v>
       </c>
       <c r="C28" t="n">
         <v>39.83499908447266</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>27.22983551025391</v>
+        <v>27.22983169555664</v>
       </c>
       <c r="C29" t="n">
         <v>43.91999816894531</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>30.14175415039062</v>
+        <v>30.14174842834473</v>
       </c>
       <c r="C30" t="n">
         <v>48.34000015258789</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>26.4909553527832</v>
+        <v>26.49095153808594</v>
       </c>
       <c r="C31" t="n">
         <v>42.48500061035156</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>22.30161666870117</v>
+        <v>22.3016242980957</v>
       </c>
       <c r="C32" t="n">
         <v>35.52000045776367</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>22.97343444824219</v>
+        <v>22.97344207763672</v>
       </c>
       <c r="C33" t="n">
         <v>36.59000015258789</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>17.63661956787109</v>
+        <v>17.63661575317383</v>
       </c>
       <c r="C34" t="n">
         <v>28.09000015258789</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>14.2746000289917</v>
+        <v>14.27460098266602</v>
       </c>
       <c r="C35" t="n">
         <v>22.47999954223633</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>14.71274185180664</v>
+        <v>14.71274757385254</v>
       </c>
       <c r="C36" t="n">
         <v>23.17000007629395</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>15.7827091217041</v>
+        <v>15.78270435333252</v>
       </c>
       <c r="C37" t="n">
         <v>24.85499954223633</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.97615242004395</v>
+        <v>13.97615528106689</v>
       </c>
       <c r="C38" t="n">
         <v>22.01000022888184</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>11.61170196533203</v>
+        <v>11.61169815063477</v>
       </c>
       <c r="C39" t="n">
         <v>18.07500076293945</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>11.83976078033447</v>
+        <v>11.83976459503174</v>
       </c>
       <c r="C40" t="n">
         <v>18.43000030517578</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.22922992706299</v>
+        <v>14.22922134399414</v>
       </c>
       <c r="C41" t="n">
         <v>21.89999961853027</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.1317663192749</v>
+        <v>14.13176345825195</v>
       </c>
       <c r="C42" t="n">
         <v>21.75</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.03466033935547</v>
+        <v>17.03465270996094</v>
       </c>
       <c r="C44" t="n">
         <v>25.95999908447266</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>18.56685829162598</v>
+        <v>18.56685256958008</v>
       </c>
       <c r="C46" t="n">
         <v>28.29500007629395</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.13323974609375</v>
+        <v>21.13324165344238</v>
       </c>
       <c r="C48" t="n">
         <v>31.95000076293945</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>21.0406436920166</v>
+        <v>21.0406379699707</v>
       </c>
       <c r="C49" t="n">
         <v>31.80999946594238</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>20.25351905822754</v>
+        <v>20.25350570678711</v>
       </c>
       <c r="C50" t="n">
         <v>30.6200008392334</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>25.25388145446777</v>
+        <v>25.25387382507324</v>
       </c>
       <c r="C52" t="n">
         <v>37.8849983215332</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>25.7171516418457</v>
+        <v>25.71716690063477</v>
       </c>
       <c r="C53" t="n">
         <v>38.58000183105469</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>23.47052574157715</v>
+        <v>23.47052764892578</v>
       </c>
       <c r="C54" t="n">
         <v>34.97499847412109</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>21.9572696685791</v>
+        <v>21.95727348327637</v>
       </c>
       <c r="C55" t="n">
         <v>32.72000122070312</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>26.32590675354004</v>
+        <v>26.32589530944824</v>
       </c>
       <c r="C56" t="n">
         <v>39.22999954223633</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.48169136047363</v>
+        <v>23.48168182373047</v>
       </c>
       <c r="C57" t="n">
         <v>34.7400016784668</v>
@@ -1562,7 +1562,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>27.87860488891602</v>
+        <v>27.87859535217285</v>
       </c>
       <c r="C58" t="n">
         <v>41.24499893188477</v>
@@ -1581,7 +1581,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.02128410339355</v>
+        <v>30.02128219604492</v>
       </c>
       <c r="C59" t="n">
         <v>44.41500091552734</v>
@@ -1600,7 +1600,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>32.78701782226562</v>
+        <v>32.78701400756836</v>
       </c>
       <c r="C60" t="n">
         <v>48.20000076293945</v>
@@ -1619,7 +1619,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>34.52500152587891</v>
+        <v>34.52500915527344</v>
       </c>
       <c r="C61" t="n">
         <v>50.75500106811523</v>
@@ -1638,7 +1638,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>36.7187385559082</v>
+        <v>36.71875381469727</v>
       </c>
       <c r="C62" t="n">
         <v>53.97999954223633</v>
@@ -1657,7 +1657,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>37.91471481323242</v>
+        <v>37.91472625732422</v>
       </c>
       <c r="C63" t="n">
         <v>55.38999938964844</v>
@@ -1676,7 +1676,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>37.94894409179688</v>
+        <v>37.94894027709961</v>
       </c>
       <c r="C64" t="n">
         <v>55.43999862670898</v>
@@ -1695,7 +1695,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>36.66207122802734</v>
+        <v>36.66207885742188</v>
       </c>
       <c r="C65" t="n">
         <v>53.56000137329102</v>
@@ -1714,7 +1714,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>35.59992218017578</v>
+        <v>35.59994125366211</v>
       </c>
       <c r="C66" t="n">
         <v>51.66999816894531</v>
@@ -1733,7 +1733,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>35.4483642578125</v>
+        <v>35.44834899902344</v>
       </c>
       <c r="C67" t="n">
         <v>51.45000076293945</v>
@@ -1771,7 +1771,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>29.81485366821289</v>
+        <v>29.81485748291016</v>
       </c>
       <c r="C69" t="n">
         <v>42.95000076293945</v>
@@ -1790,7 +1790,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>24.64324188232422</v>
+        <v>24.64325141906738</v>
       </c>
       <c r="C70" t="n">
         <v>35.5</v>
@@ -1809,7 +1809,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>31.11296844482422</v>
+        <v>31.11297798156738</v>
       </c>
       <c r="C71" t="n">
         <v>44.81999969482422</v>
@@ -1828,7 +1828,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>31.41129875183105</v>
+        <v>31.41130638122559</v>
       </c>
       <c r="C72" t="n">
         <v>44.90999984741211</v>
@@ -1847,7 +1847,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>30.44608879089355</v>
+        <v>30.44610214233398</v>
       </c>
       <c r="C73" t="n">
         <v>43.52999877929688</v>
@@ -1885,7 +1885,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>36.78371429443359</v>
+        <v>36.7837028503418</v>
       </c>
       <c r="C75" t="n">
         <v>52.18999862670898</v>
@@ -1904,7 +1904,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>35.1203727722168</v>
+        <v>35.12035751342773</v>
       </c>
       <c r="C76" t="n">
         <v>49.83000183105469</v>
@@ -1923,7 +1923,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>33.95744323730469</v>
+        <v>33.95744705200195</v>
       </c>
       <c r="C77" t="n">
         <v>48.18000030517578</v>
@@ -1942,7 +1942,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>30.30873107910156</v>
+        <v>30.3087329864502</v>
       </c>
       <c r="C78" t="n">
         <v>42.65999984741211</v>
@@ -1961,7 +1961,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>28.156005859375</v>
+        <v>28.15600776672363</v>
       </c>
       <c r="C79" t="n">
         <v>39.63000106811523</v>
@@ -1980,7 +1980,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>31.14709281921387</v>
+        <v>31.14709091186523</v>
       </c>
       <c r="C80" t="n">
         <v>43.84000015258789</v>
@@ -1999,7 +1999,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>32.05146408081055</v>
+        <v>32.05146026611328</v>
       </c>
       <c r="C81" t="n">
         <v>44.72000122070312</v>
@@ -2018,7 +2018,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>33.87907409667969</v>
+        <v>33.87907791137695</v>
       </c>
       <c r="C82" t="n">
         <v>47.27000045776367</v>
@@ -2037,7 +2037,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>34.12123870849609</v>
+        <v>34.12125396728516</v>
       </c>
       <c r="C83" t="n">
         <v>47.22000122070312</v>
@@ -2056,7 +2056,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>37.6909065246582</v>
+        <v>37.69091033935547</v>
       </c>
       <c r="C84" t="n">
         <v>52.15999984741211</v>
@@ -2075,7 +2075,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>39.15056228637695</v>
+        <v>39.15056610107422</v>
       </c>
       <c r="C85" t="n">
         <v>54.18000030517578</v>
@@ -2094,7 +2094,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>41.15216445922852</v>
+        <v>41.15217208862305</v>
       </c>
       <c r="C86" t="n">
         <v>56.95000076293945</v>
@@ -2138,7 +2138,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>44.55820846557617</v>
+        <v>44.55820465087891</v>
       </c>
       <c r="C88" t="n">
         <v>61.25</v>
@@ -2163,7 +2163,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>44.67462158203125</v>
+        <v>44.67460632324219</v>
       </c>
       <c r="C89" t="n">
         <v>61.40999984741211</v>
@@ -2188,7 +2188,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>48.40036773681641</v>
+        <v>48.4003791809082</v>
       </c>
       <c r="C90" t="n">
         <v>66.05999755859375</v>
@@ -2238,7 +2238,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>50.51778411865234</v>
+        <v>50.51779174804688</v>
       </c>
       <c r="C92" t="n">
         <v>68.94999694824219</v>
@@ -2263,7 +2263,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>46.67716217041016</v>
+        <v>46.67716598510742</v>
       </c>
       <c r="C93" t="n">
         <v>63.31999969482422</v>
@@ -2288,7 +2288,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>50.74631118774414</v>
+        <v>50.74632263183594</v>
       </c>
       <c r="C94" t="n">
         <v>68.83999633789062</v>
@@ -2313,7 +2313,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>52.32248306274414</v>
+        <v>52.32249069213867</v>
       </c>
       <c r="C95" t="n">
         <v>70.55999755859375</v>
@@ -2338,7 +2338,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>53.87971115112305</v>
+        <v>53.87970733642578</v>
       </c>
       <c r="C96" t="n">
         <v>72.66000366210938</v>
@@ -2363,7 +2363,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>56.44541549682617</v>
+        <v>56.44541931152344</v>
       </c>
       <c r="C97" t="n">
         <v>76.12000274658203</v>
@@ -2388,7 +2388,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>54.19855880737305</v>
+        <v>54.19858551025391</v>
       </c>
       <c r="C98" t="n">
         <v>73.08999633789062</v>
@@ -2413,7 +2413,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>55.39984893798828</v>
+        <v>55.39985656738281</v>
       </c>
       <c r="C99" t="n">
         <v>74.70999908447266</v>
@@ -2442,7 +2442,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>56.07316970825195</v>
+        <v>56.07318878173828</v>
       </c>
       <c r="C100" t="n">
         <v>75.12000274658203</v>
@@ -2471,7 +2471,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>54.22197723388672</v>
+        <v>54.22198104858398</v>
       </c>
       <c r="C101" t="n">
         <v>72.63999938964844</v>
@@ -2529,7 +2529,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>58.00212097167969</v>
+        <v>58.00210189819336</v>
       </c>
       <c r="C103" t="n">
         <v>77.18000030517578</v>
@@ -2558,7 +2558,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>51.40341186523438</v>
+        <v>51.40340423583984</v>
       </c>
       <c r="C104" t="n">
         <v>67.91999816894531</v>
@@ -2587,7 +2587,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>52.83380508422852</v>
+        <v>52.83379745483398</v>
       </c>
       <c r="C105" t="n">
         <v>69.80999755859375</v>
@@ -2645,7 +2645,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>51.75909805297852</v>
+        <v>51.75911712646484</v>
       </c>
       <c r="C107" t="n">
         <v>68.38999938964844</v>
@@ -2674,7 +2674,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>51.70549011230469</v>
+        <v>51.70547866821289</v>
       </c>
       <c r="C108" t="n">
         <v>67.83000183105469</v>
@@ -2703,7 +2703,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>51.8045768737793</v>
+        <v>51.8045654296875</v>
       </c>
       <c r="C109" t="n">
         <v>67.95999908447266</v>
@@ -2732,7 +2732,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>48.0922737121582</v>
+        <v>48.09228134155273</v>
       </c>
       <c r="C110" t="n">
         <v>63.09000015258789</v>
@@ -2761,7 +2761,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>54.1295280456543</v>
+        <v>54.12954330444336</v>
       </c>
       <c r="C111" t="n">
         <v>71.01000213623047</v>
@@ -2790,7 +2790,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>52.20154571533203</v>
+        <v>52.20155334472656</v>
       </c>
       <c r="C112" t="n">
         <v>67.94000244140625</v>
@@ -2819,7 +2819,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>53.22954177856445</v>
+        <v>53.22953796386719</v>
       </c>
       <c r="C113" t="n">
         <v>68.73000335693359</v>
@@ -2848,7 +2848,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>55.44451904296875</v>
+        <v>55.44452285766602</v>
       </c>
       <c r="C114" t="n">
         <v>71.58999633789062</v>
@@ -2877,7 +2877,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>52.26920318603516</v>
+        <v>52.26919174194336</v>
       </c>
       <c r="C115" t="n">
         <v>67.48999786376953</v>
@@ -2906,7 +2906,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>47.33888244628906</v>
+        <v>47.33889007568359</v>
       </c>
       <c r="C116" t="n">
         <v>60.58000183105469</v>
@@ -2935,7 +2935,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>44.5882453918457</v>
+        <v>44.58825302124023</v>
       </c>
       <c r="C117" t="n">
         <v>57.06000137329102</v>
@@ -2964,7 +2964,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>40.08722686767578</v>
+        <v>40.08723068237305</v>
       </c>
       <c r="C118" t="n">
         <v>51.29999923706055</v>
@@ -3022,7 +3022,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>45.89268112182617</v>
+        <v>45.89268493652344</v>
       </c>
       <c r="C120" t="n">
         <v>58.15999984741211</v>
@@ -3051,7 +3051,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>41.06352996826172</v>
+        <v>41.06353378295898</v>
       </c>
       <c r="C121" t="n">
         <v>52.04000091552734</v>
@@ -3080,7 +3080,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>39.85623931884766</v>
+        <v>39.85623550415039</v>
       </c>
       <c r="C122" t="n">
         <v>50.5099983215332</v>
@@ -3138,7 +3138,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>49.85499572753906</v>
+        <v>49.85498809814453</v>
       </c>
       <c r="C124" t="n">
         <v>62.56000137329102</v>
@@ -3167,7 +3167,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>50.42080688476562</v>
+        <v>50.42081069946289</v>
       </c>
       <c r="C125" t="n">
         <v>63.27000045776367</v>
@@ -3196,7 +3196,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>49.56021881103516</v>
+        <v>49.56021499633789</v>
       </c>
       <c r="C126" t="n">
         <v>61.63000106811523</v>
@@ -3225,7 +3225,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>48.03231811523438</v>
+        <v>48.03230667114258</v>
       </c>
       <c r="C127" t="n">
         <v>59.72999954223633</v>
@@ -3283,7 +3283,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>53.9893913269043</v>
+        <v>53.98939514160156</v>
       </c>
       <c r="C129" t="n">
         <v>66.54000091552734</v>
@@ -3312,7 +3312,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>53.31593704223633</v>
+        <v>53.31595230102539</v>
       </c>
       <c r="C130" t="n">
         <v>65.70999908447266</v>
@@ -3341,7 +3341,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>51.74186325073242</v>
+        <v>51.74185943603516</v>
       </c>
       <c r="C131" t="n">
         <v>63.77000045776367</v>
@@ -3370,7 +3370,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>54.47509384155273</v>
+        <v>54.47507476806641</v>
       </c>
       <c r="C132" t="n">
         <v>66.51000213623047</v>
@@ -3399,7 +3399,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>54.95013809204102</v>
+        <v>54.95011901855469</v>
       </c>
       <c r="C133" t="n">
         <v>67.08999633789062</v>
@@ -3428,7 +3428,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>57.97246551513672</v>
+        <v>57.97243499755859</v>
       </c>
       <c r="C134" t="n">
         <v>70.77999877929688</v>
@@ -3457,7 +3457,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>58.95528793334961</v>
+        <v>58.95529937744141</v>
       </c>
       <c r="C135" t="n">
         <v>71.98000335693359</v>
@@ -3486,7 +3486,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>61.23430252075195</v>
+        <v>61.23429489135742</v>
       </c>
       <c r="C136" t="n">
         <v>74.15000152587891</v>
@@ -3515,7 +3515,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>62.46472549438477</v>
+        <v>62.46475219726562</v>
       </c>
       <c r="C137" t="n">
         <v>75.63999938964844</v>
@@ -3544,7 +3544,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>64.40277862548828</v>
+        <v>64.40279388427734</v>
       </c>
       <c r="C138" t="n">
         <v>77.37999725341797</v>
@@ -3573,7 +3573,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>64.77732086181641</v>
+        <v>64.77731323242188</v>
       </c>
       <c r="C139" t="n">
         <v>77.83000183105469</v>
@@ -3602,7 +3602,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>65.12687683105469</v>
+        <v>65.12689208984375</v>
       </c>
       <c r="C140" t="n">
         <v>78.25</v>
@@ -3631,7 +3631,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>60.21180725097656</v>
+        <v>60.2118034362793</v>
       </c>
       <c r="C141" t="n">
         <v>71.76000213623047</v>
@@ -3660,7 +3660,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>64.43231964111328</v>
+        <v>64.43234252929688</v>
       </c>
       <c r="C142" t="n">
         <v>76.79000091552734</v>
@@ -3689,7 +3689,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>67.14255523681641</v>
+        <v>67.14253234863281</v>
       </c>
       <c r="C143" t="n">
         <v>80.01999664306641</v>
@@ -3747,7 +3747,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>66.78667449951172</v>
+        <v>66.78670501708984</v>
       </c>
       <c r="C145" t="n">
         <v>79.01000213623047</v>
@@ -3776,7 +3776,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>70.9793701171875</v>
+        <v>70.97935485839844</v>
       </c>
       <c r="C146" t="n">
         <v>83.97000122070312</v>
@@ -3805,7 +3805,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>68.21522521972656</v>
+        <v>68.21524047851562</v>
       </c>
       <c r="C147" t="n">
         <v>80.69999694824219</v>
@@ -3863,7 +3863,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>63.94252777099609</v>
+        <v>63.94253158569336</v>
       </c>
       <c r="C149" t="n">
         <v>75.02999877929688</v>
@@ -3892,7 +3892,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>65.86041259765625</v>
+        <v>65.86039733886719</v>
       </c>
       <c r="C150" t="n">
         <v>76.58000183105469</v>
@@ -3921,7 +3921,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>64.27796936035156</v>
+        <v>64.27796173095703</v>
       </c>
       <c r="C151" t="n">
         <v>74.73999786376953</v>
@@ -3979,7 +3979,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>71.50213623046875</v>
+        <v>71.50215148925781</v>
       </c>
       <c r="C153" t="n">
         <v>83.13999938964844</v>
@@ -4008,7 +4008,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>74.58959197998047</v>
+        <v>74.58963775634766</v>
       </c>
       <c r="C154" t="n">
         <v>86.73000335693359</v>
@@ -4037,7 +4037,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>61.6376953125</v>
+        <v>61.6377067565918</v>
       </c>
       <c r="C155" t="n">
         <v>71.66999816894531</v>
@@ -4066,7 +4066,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>66.17001342773438</v>
+        <v>66.17000579833984</v>
       </c>
       <c r="C156" t="n">
         <v>76.94000244140625</v>
@@ -4095,7 +4095,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>59.04903793334961</v>
+        <v>59.04905319213867</v>
       </c>
       <c r="C157" t="n">
         <v>68.66000366210938</v>
@@ -4124,7 +4124,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>65.57658386230469</v>
+        <v>65.57659912109375</v>
       </c>
       <c r="C158" t="n">
         <v>76.25</v>
@@ -4153,7 +4153,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>68.60387420654297</v>
+        <v>68.60386657714844</v>
       </c>
       <c r="C159" t="n">
         <v>79.76999664306641</v>
@@ -4211,7 +4211,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>71.85717010498047</v>
+        <v>71.857177734375</v>
       </c>
       <c r="C161" t="n">
         <v>82.81999969482422</v>
@@ -4269,7 +4269,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>72.88809967041016</v>
+        <v>72.88808441162109</v>
       </c>
       <c r="C163" t="n">
         <v>83.27999877929688</v>
@@ -4298,7 +4298,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>71.93409729003906</v>
+        <v>71.93410491943359</v>
       </c>
       <c r="C164" t="n">
         <v>82.19000244140625</v>
@@ -4385,7 +4385,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>77.52822875976562</v>
+        <v>77.52825164794922</v>
       </c>
       <c r="C167" t="n">
         <v>87.11000061035156</v>
@@ -4414,7 +4414,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>82.32538604736328</v>
+        <v>82.32536315917969</v>
       </c>
       <c r="C168" t="n">
         <v>92.5</v>
@@ -4443,7 +4443,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>84.30119323730469</v>
+        <v>84.30116271972656</v>
       </c>
       <c r="C169" t="n">
         <v>94.72000122070312</v>
@@ -4472,7 +4472,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>84.07868194580078</v>
+        <v>84.07869720458984</v>
       </c>
       <c r="C170" t="n">
         <v>94.47000122070312</v>
@@ -4530,7 +4530,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>69.74790191650391</v>
+        <v>69.74789428710938</v>
       </c>
       <c r="C172" t="n">
         <v>77.69000244140625</v>
@@ -4559,7 +4559,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>74.96396636962891</v>
+        <v>74.96395874023438</v>
       </c>
       <c r="C173" t="n">
         <v>83.5</v>
@@ -4588,7 +4588,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>76.29273223876953</v>
+        <v>76.292724609375</v>
       </c>
       <c r="C174" t="n">
         <v>84.90000152587891</v>
@@ -4617,7 +4617,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>78.61119079589844</v>
+        <v>78.61115264892578</v>
       </c>
       <c r="C175" t="n">
         <v>87.48000335693359</v>
@@ -4646,7 +4646,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>83.6883544921875</v>
+        <v>83.68836975097656</v>
       </c>
       <c r="C176" t="n">
         <v>93.12999725341797</v>
@@ -4704,7 +4704,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>92.34341430664062</v>
+        <v>92.34343719482422</v>
       </c>
       <c r="C178" t="n">
         <v>102.0299987792969</v>
@@ -4733,7 +4733,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>93.93634796142578</v>
+        <v>93.93631744384766</v>
       </c>
       <c r="C179" t="n">
         <v>103.7900009155273</v>
@@ -4791,7 +4791,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>109.4888153076172</v>
+        <v>109.4888076782227</v>
       </c>
       <c r="C181" t="n">
         <v>120.1399993896484</v>
@@ -4820,7 +4820,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>107.2651443481445</v>
+        <v>107.26513671875</v>
       </c>
       <c r="C182" t="n">
         <v>117.6999969482422</v>
@@ -4849,7 +4849,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>118.6478271484375</v>
+        <v>118.6478042602539</v>
       </c>
       <c r="C183" t="n">
         <v>130.1900024414062</v>
@@ -4878,7 +4878,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>126.7045974731445</v>
+        <v>126.7046203613281</v>
       </c>
       <c r="C184" t="n">
         <v>138.2799987792969</v>
@@ -4907,7 +4907,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>130.9654235839844</v>
+        <v>130.9653778076172</v>
       </c>
       <c r="C185" t="n">
         <v>142.9299926757812</v>
@@ -4936,7 +4936,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>133.798828125</v>
+        <v>133.7988891601562</v>
       </c>
       <c r="C186" t="n">
         <v>145.25</v>
@@ -4994,7 +4994,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>145.5897216796875</v>
+        <v>145.5897369384766</v>
       </c>
       <c r="C188" t="n">
         <v>158.0500030517578</v>
@@ -5023,7 +5023,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>155.7963562011719</v>
+        <v>155.7963409423828</v>
       </c>
       <c r="C189" t="n">
         <v>168.3600006103516</v>
@@ -5052,7 +5052,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>138.1679534912109</v>
+        <v>138.1679077148438</v>
       </c>
       <c r="C190" t="n">
         <v>149.3099975585938</v>
@@ -5081,7 +5081,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>152.4649505615234</v>
+        <v>152.4649353027344</v>
       </c>
       <c r="C191" t="n">
         <v>164.7599945068359</v>
@@ -5110,7 +5110,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>150.6219024658203</v>
+        <v>150.6218719482422</v>
       </c>
       <c r="C192" t="n">
         <v>162.0599975585938</v>
@@ -5139,7 +5139,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>160.6224517822266</v>
+        <v>160.6224670410156</v>
       </c>
       <c r="C193" t="n">
         <v>172.8200073242188</v>
@@ -5168,7 +5168,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>147.2480773925781</v>
+        <v>147.248046875</v>
       </c>
       <c r="C194" t="n">
         <v>158.4299926757812</v>
@@ -5197,7 +5197,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>143.4002838134766</v>
+        <v>143.4002685546875</v>
       </c>
       <c r="C195" t="n">
         <v>154.2899932861328</v>
@@ -5226,7 +5226,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>141.8191833496094</v>
+        <v>141.8192138671875</v>
       </c>
       <c r="C196" t="n">
         <v>151.7599945068359</v>
@@ -5255,7 +5255,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>135.5206909179688</v>
+        <v>135.5207061767578</v>
       </c>
       <c r="C197" t="n">
         <v>145.0200042724609</v>
@@ -5284,7 +5284,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>130.2705841064453</v>
+        <v>130.2705688476562</v>
       </c>
       <c r="C198" t="n">
         <v>138.6000061035156</v>
@@ -5313,7 +5313,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>118.4184188842773</v>
+        <v>118.4184265136719</v>
       </c>
       <c r="C199" t="n">
         <v>125.9899978637695</v>
@@ -5342,7 +5342,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>139.4722442626953</v>
+        <v>139.4722595214844</v>
       </c>
       <c r="C200" t="n">
         <v>148.3899993896484</v>
@@ -5371,7 +5371,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>129.1287689208984</v>
+        <v>129.1287536621094</v>
       </c>
       <c r="C201" t="n">
         <v>136.6399993896484</v>
@@ -5400,7 +5400,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>126.0290222167969</v>
+        <v>126.0290679931641</v>
       </c>
       <c r="C202" t="n">
         <v>133.3600006103516</v>
@@ -5458,7 +5458,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>155.2599639892578</v>
+        <v>155.2599945068359</v>
       </c>
       <c r="C204" t="n">
         <v>163.4499969482422</v>
@@ -5516,7 +5516,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>154.0821380615234</v>
+        <v>154.0821228027344</v>
       </c>
       <c r="C206" t="n">
         <v>162.2100067138672</v>
@@ -5545,7 +5545,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>166.1647338867188</v>
+        <v>166.1647491455078</v>
       </c>
       <c r="C207" t="n">
         <v>174.9299926757812</v>
@@ -5632,7 +5632,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>168.7723083496094</v>
+        <v>168.7722778320312</v>
       </c>
       <c r="C210" t="n">
         <v>175.8999938964844</v>
@@ -5661,7 +5661,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>192.9511566162109</v>
+        <v>192.9511260986328</v>
       </c>
       <c r="C211" t="n">
         <v>201.1000061035156</v>
@@ -5719,7 +5719,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>221.9141235351562</v>
+        <v>221.9141693115234</v>
       </c>
       <c r="C213" t="n">
         <v>230.3699951171875</v>
@@ -5748,7 +5748,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>205.4514617919922</v>
+        <v>205.4514312744141</v>
       </c>
       <c r="C214" t="n">
         <v>213.2799987792969</v>
@@ -5835,7 +5835,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>232.9072418212891</v>
+        <v>232.9072113037109</v>
       </c>
       <c r="C217" t="n">
         <v>240.8200073242188</v>
@@ -5864,7 +5864,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>237.9944000244141</v>
+        <v>237.9943695068359</v>
       </c>
       <c r="C218" t="n">
         <v>246.0800018310547</v>
@@ -5893,7 +5893,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>279.5041809082031</v>
+        <v>279.504150390625</v>
       </c>
       <c r="C219" t="n">
         <v>289</v>
@@ -5922,7 +5922,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>303.3529968261719</v>
+        <v>303.3530578613281</v>
       </c>
       <c r="C220" t="n">
         <v>312.6799926757812</v>
@@ -5951,7 +5951,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>308.7665100097656</v>
+        <v>308.7666015625</v>
       </c>
       <c r="C221" t="n">
         <v>318.260009765625</v>
@@ -5980,7 +5980,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>323.8869934082031</v>
+        <v>323.8870239257812</v>
       </c>
       <c r="C222" t="n">
         <v>332.8500061035156</v>
@@ -6009,7 +6009,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>305.1067504882812</v>
+        <v>305.1067199707031</v>
       </c>
       <c r="C223" t="n">
         <v>313.5499877929688</v>
@@ -6038,7 +6038,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>296.5826416015625</v>
+        <v>296.5826721191406</v>
       </c>
       <c r="C224" t="n">
         <v>304.7900085449219</v>
@@ -6067,7 +6067,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>299.6701049804688</v>
+        <v>299.6701354980469</v>
       </c>
       <c r="C225" t="n">
         <v>306.9299926757812</v>
@@ -6096,7 +6096,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>323.600341796875</v>
+        <v>323.6004028320312</v>
       </c>
       <c r="C226" t="n">
         <v>331.4400024414062</v>
@@ -6154,7 +6154,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>367.5714721679688</v>
+        <v>367.5715026855469</v>
       </c>
       <c r="C228" t="n">
         <v>375.4200134277344</v>
@@ -6183,7 +6183,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>324.9319458007812</v>
+        <v>324.9319152832031</v>
       </c>
       <c r="C229" t="n">
         <v>331.8699951171875</v>
@@ -6212,7 +6212,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>319.6154479980469</v>
+        <v>319.6155090332031</v>
       </c>
       <c r="C230" t="n">
         <v>326.4400024414062</v>
@@ -6241,7 +6241,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>287.1878662109375</v>
+        <v>287.1878356933594</v>
       </c>
       <c r="C231" t="n">
         <v>293.3200073242188</v>
@@ -6270,7 +6270,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>267.1219177246094</v>
+        <v>267.1218872070312</v>
       </c>
       <c r="C232" t="n">
         <v>271.8299865722656</v>
@@ -6299,7 +6299,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>289.2715759277344</v>
+        <v>289.2715454101562</v>
       </c>
       <c r="C233" t="n">
         <v>294.3699951171875</v>
@@ -6328,7 +6328,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>315.7498168945312</v>
+        <v>315.7498474121094</v>
       </c>
       <c r="C234" t="n">
         <v>320.2000122070312</v>
@@ -6386,7 +6386,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>379.3731079101562</v>
+        <v>379.3731384277344</v>
       </c>
       <c r="C236" t="n">
         <v>384.7200012207031</v>
@@ -6415,7 +6415,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>345.290283203125</v>
+        <v>345.2902526855469</v>
       </c>
       <c r="C237" t="n">
         <v>349.1400146484375</v>
@@ -6444,7 +6444,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>370.1233520507812</v>
+        <v>370.1233825683594</v>
       </c>
       <c r="C238" t="n">
         <v>374.25</v>
@@ -6502,7 +6502,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>343.0205688476562</v>
+        <v>343.0205993652344</v>
       </c>
       <c r="C240" t="n">
         <v>345.8900146484375</v>
